--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Hilti Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
+          <t>https://www.indeed.com/viewjob?jk=9998eca1dfe5af6d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc189598639baae0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
+          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-3</t>
+          <t>AWS/Python Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
+          <t>https://www.indeed.com/viewjob?jk=188fa78b94de887a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Testing Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
+          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Kafka Testing Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baafabe84b28d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,54 +1476,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9baafabe84b28d4a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Architect 3 (529501460R)</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,49 +2036,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,172 +2351,172 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect 3 (529501460R)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
+          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,172 +2946,172 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
+          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
+          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
+          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,40 +4556,1055 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Barrington, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Caldwell, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>API Security IAM Engineer</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,69 +2271,69 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
+          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
+          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
+          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
+          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
+          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
+          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
+          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
+          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
+          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
+          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
+          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>
       </c>
     </row>
@@ -5438,17 +5438,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,40 +5571,75 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>API Security IAM Engineer</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -5333,17 +5333,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>API Security IAM Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>API Security IAM Engineer</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
+          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baafabe84b28d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9baafabe84b28d4a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
@@ -2008,52 +2008,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,42 +2351,42 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Architect 3 (529501460R)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,322 +2726,322 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,172 +3156,172 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,942 +3366,942 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Enterprise Architect 3 (529501460R)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,172 +4836,172 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,102 +5116,102 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,59 +5256,59 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>API Security IAM Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080dd790549ca45e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,17 +5631,1802 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Parlin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Rehoboth Beach, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Dayton, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Derby, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Newmarket, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Stafford, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Clinton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Barrington, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Caldwell, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Woonsocket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98652de9480b1951</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Integration Platform</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
           <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
@@ -1763,25 +1763,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,69 +2376,69 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Enterprise Architect 3 (529501460R)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Enterprise Architect 3 (529501460R)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,42 +4546,42 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
+          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
+          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
         </is>
       </c>
     </row>
@@ -4988,12 +4988,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5023,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Marion, IA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Liberty, MO, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
+          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Parlin, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
+          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Parlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
+          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
+          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Rehoboth Beach, DE, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
+          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Dayton, MN, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
+          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Derby, CT, US USA</t>
+          <t>Dayton, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Newmarket, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Derby, CT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Stafford, VA, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
+          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Stafford, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Clinton, MS, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Clinton, MS, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
+          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
+          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Medway, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
+          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Medway, MA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
+          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
+          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Watson, AR, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Newport, MI, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
+          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Watson, AR, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
+          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hudson, WI, US USA</t>
+          <t>Newport, MI, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Barrington, RI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Hudson, WI, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
+          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
+          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Monrovia, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
+          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Caldwell, ID, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
+          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98652de9480b1951</t>
+          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integration Platform</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
+          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=98652de9480b1951</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,15 +7416,85 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baafabe84b28d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,42 +2386,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Enterprise Architect 3 (529501460R)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e395e8c2af5189f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,42 +4476,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,67 +4521,67 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187ae0b8f8fd0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4918,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491fbc29551dfb6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ff15918eb570db</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89695ca4c4735314</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,77 +5036,77 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Scala, Kafka, PostgreSQL, ETL, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d33a526b72871</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,102 +5151,102 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5312,11 +5312,11 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,1967 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Application Developer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>PENNYMAC</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Carrollton, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f68999e3a08b34</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Fargo, ND, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7568ad4f68a794</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Tyler, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52238de5d8e31e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Marion, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9a9a37ab0d96f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Liberty, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f136125e04b66c73</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4918daca312f2244</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=779fab7c29fa86f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82696b1123770e7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Parlin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=784cdfc19af10bef</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=478b67e11e517a6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd2f8883c7c2c58</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=196b31dc98641b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Rehoboth Beach, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57eefa4ab67cd697</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32c44b4cc154e674</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Dayton, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b9517a01a6afc</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=973b964a0f591ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Derby, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec51f8f969e14cf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Newmarket, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5652ebc9bf49bf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56132a79b8e257a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Stafford, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29d898862048a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcf87f4ae954a87</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8956a3adf5ea0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Frankfort, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcf4f0bd1ef1d34</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Clinton, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0468b99fb72fd82f</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcab207377fb1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2930761b280e653e</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a421856a8539fed6</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Medway, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=782f328c04380066</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=352c07120666e5c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42baffc4c7805e28</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Missoula, MT, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46833a029042b4bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Watson, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17c5fd0139ae8bc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Newport, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc35ec9058fa3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfb102c7ccf172b</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Hudson, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85a679038244e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Barrington, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1aea8ceb4ec114a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Boulder, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90340400c0a73eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbad1c85611a5fa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b4e01b96f96859</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7abf686b4b05726</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Monrovia, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b09b6d139d7d5dc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Richland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31b7be7f3829a65a</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7da40b1f46a195</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Caldwell, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d796774718fde3c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Pierre, SD, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be750e2f0e29fd59</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=843cb19e01616170</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>ISHIR</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Woonsocket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98652de9480b1951</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Integration Platform</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ac2a746d527ccc</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Streaming Data</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Dudek</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Kafka API Engineer</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,52 +1098,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
@@ -2008,52 +2008,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,69 +2341,69 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,42 +4476,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,14 +4661,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,59 +5046,59 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,15 +5526,50 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Sr. Palantir Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>A2R Global Private Limited</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Enterprise Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,147 +4511,147 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,67 +5081,67 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,15 +5561,155 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,69 +2516,69 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,42 +4651,42 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
@@ -5228,52 +5228,52 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,15 +5701,50 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -5438,17 +5438,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Sr. Palantir Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>A2R Global Private Limited</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Palantir Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A2R Global Private Limited</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer II</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6173d48ac796a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,69 +2551,69 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,24 +4651,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,49 +4696,49 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4752,11 +4752,11 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,24 +5036,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5076,19 +5076,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5111,29 +5111,29 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,67 +5256,67 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,15 +5736,120 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
@@ -1413,60 +1413,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Sr. Palantir Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>A2R Global Private Limited</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Palantir Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A2R Global Private Limited</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,104 +2516,104 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
@@ -4563,25 +4563,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,67 +4696,67 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,172 +4976,172 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,67 +5186,67 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5277,11 +5277,11 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,435 +5421,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Delta Dental Ins.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Ensono</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Kafka Azure Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Azure Stack Data Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>AAON</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Dudek</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Kafka API Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Streaming Data</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS/Python Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188fa78b94de887a</t>
+          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>AWS/Python Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
+          <t>https://www.indeed.com/viewjob?jk=188fa78b94de887a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -666,29 +666,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-3</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
+          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
@@ -1693,52 +1693,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc67f182252edbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
@@ -2463,70 +2463,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Full Stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,69 +4511,69 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4796,29 +4796,29 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,42 +4941,42 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps, Python, SQL, Java</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c1542c9d68f0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
+          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -701,72 +701,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Testing Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer</t>
+          <t>Kafka Testing Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
+          <t>Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,104 +1676,104 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Palantir Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A2R Global Private Limited</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2477,38 +2477,38 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Full Stack Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,42 +4511,42 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,59 +4591,59 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,129 +4941,129 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,15 +5421,155 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -678,95 +678,95 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Kafka Testing Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
+          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Testing Engineer</t>
+          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Timestream, S3, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c312e3c7f58bcc51</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,77 +951,77 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
@@ -1413,60 +1413,60 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior AI Engineer, IT Solutions 1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Full Stack Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373084662062e4b3</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
@@ -4563,25 +4563,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,59 +4591,59 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea574ef4d474030</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961aed70d2a33b06</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
+          <t>https://www.indeed.com/viewjob?jk=76a633e7c45d5fa0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II (Hybrid Work Schedule)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e509811f28e16</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
         </is>
       </c>
     </row>
@@ -1028,87 +1028,87 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86b9bb645724e6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>POS and Systems Integration Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Silver Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeab26e4dddac1a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Child Support - Senior Full Stack AI/Java Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Prospect Infosys Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d82ce6deb44503</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
         </is>
       </c>
     </row>
@@ -2498,25 +2498,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, IT Solutions 1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior AI Engineer, IT Solutions 1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,77 +4546,77 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4901,19 +4901,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4936,29 +4936,29 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
@@ -5438,17 +5438,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86b9bb645724e6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>POS and Systems Integration Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Silver Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86b9bb645724e6</t>
+          <t>https://www.indeed.com/viewjob?jk=eeab26e4dddac1a9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>POS and Systems Integration Administrator</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Silver Creek, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeab26e4dddac1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
@@ -1698,55 +1698,55 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>System Integration Test Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BGIT India Private Limited</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hudson, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=426d1d0d6a93918c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Child Support - Senior Full Stack AI/Java Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prospect Infosys Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d82ce6deb44503</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Child Support - Senior Full Stack AI/Java Developer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Prospect Infosys Inc</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d82ce6deb44503</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, IT Solutions 1</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior AI Engineer, IT Solutions 1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
@@ -4598,25 +4598,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
@@ -5018,52 +5018,52 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Full Stack Software Engineer - Observability</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,52 +5526,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, Splunk, CI/CD, Docker, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=08caee1edcf07e86</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Kafka Pre Sales Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
+          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6ad57eba624292</t>
+          <t>https://www.indeed.com/viewjob?jk=17c87f0de0ddb952</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Backend Software Engineer III - API Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15325ad687b27337</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - API Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>D&amp;G Support Services, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, API Gateway, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1c3ba542522bad</t>
+          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D&amp;G Support Services, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e360184b3be6da</t>
+          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POS and Systems Integration Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Silver Creek, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeab26e4dddac1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
         </is>
       </c>
     </row>
@@ -1663,47 +1663,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f9ad9e43193a20</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97eb9417ef8ebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palomar College</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe8d5c4946b355</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Child Support - Senior Full Stack AI/Java Developer</t>
+          <t>Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Prospect Infosys Inc</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d82ce6deb44503</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdaab0a9b0d0cc5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>EXECUTIVE - Senior Full Stack AI/Java Developer - Raleigh, NC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=6954fce33a80b920</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Engineer I-Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Data Platform Engineer-1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
+          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
+          <t>https://www.indeed.com/viewjob?jk=0fe0f50a558682d2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform-DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NXLog</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
+          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9886d247b0ec7a02</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Platform-DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NXLog</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7328772f0c8abe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=659e59333f0b2e8c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Barbara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc978b16714d0d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
+          <t>https://www.indeed.com/viewjob?jk=9649d08cb62a9ac0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEARLY</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
+          <t>https://www.indeed.com/viewjob?jk=56c2a6bb8439d052</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WeGo Public Transit</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Barbara, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
+          <t>https://www.indeed.com/viewjob?jk=52fbd92226aade92</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, IT Solutions 1</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
+          <t>https://www.indeed.com/viewjob?jk=3e77317858ff838d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>PEARLY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9737f288d965528f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WeGo Public Transit</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7d3460f6613884</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Engineer, IT Solutions 1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Celestica</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,102 +4591,102 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,24 +4756,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,29 +4861,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>FullPath</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,24 +4966,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=43ff07c409bb7f44</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5006,37 +5006,37 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,102 +5081,102 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Azure Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Observability</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,15 +5526,225 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>New York Post</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Reporting Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer - Observability</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, ETL, Splunk, CI/CD, Docker, Kubernetes, Git, Datadog</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=08caee1edcf07e86</t>
         </is>

--- a/results/job_matches_2026-03-03.xlsx
+++ b/results/job_matches_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Software Engineer in Test III - Data Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Emburse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
+          <t>https://www.indeed.com/viewjob?jk=450782bf82b6fc2f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Testing Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9878976e87f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=afe6c49fa2525821</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Pre Sales Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,38 +762,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, Athena, S3, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97773a93c62e6c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4725509304854f9e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - AI Practice Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=98e9bc7cd1938bfd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Dask, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8753556282d7d43c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6b50f861d0e9c5</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer – Engineering Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f923b35d6b28f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Engineering Analytics</t>
+          <t>Cloud Engineer- Remote US</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32e7d55317e214e</t>
+          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer- Remote US</t>
+          <t>Sr Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25625460182eb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Analyst, Risk Data Engineering</t>
+          <t>Software Engineer II,</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, ECS, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bc5a9a6e784515</t>
+          <t>https://www.indeed.com/viewjob?jk=28ab3491bb9f5589</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, HBase</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55fe2f4c3849aee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d093becf8bff38</t>
+          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df93d33bb1e254</t>
+          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Cloud Software Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b63f4ef510667a</t>
+          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>Engineer – Drug Delivery Device Development</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72630d316687619c</t>
+          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer – Drug Delivery Device Development</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c397d8c90a9884</t>
+          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b12dfc8a5459a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d49d017dead0cec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Data Engineer - Kafka Connect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1a55e3e9d2956f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Kafka Connect</t>
+          <t>Production Engineer (Oracle/Snowflake/Python)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5df3111682f7946</t>
+          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Production Engineer (Oracle/Snowflake/Python)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7435b55b7adadc42</t>
+          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Associate/Consultant Engineer - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Rancho BioSciences</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351825ec13a4ff81</t>
+          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86b9bb645724e6</t>
+          <t>https://www.indeed.com/viewjob?jk=80460d4e824e28cc</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate/Consultant Engineer - Remote</t>
+          <t>AI Engineer/Architect-IFS Cloud</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rancho BioSciences</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd467efc7d909226</t>
+          <t>https://www.indeed.com/viewjob?jk=0c154c59806de726</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PDM Implementation Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3576de9e88dd4c5c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a53eba2ddb1389c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
+          <t>https://www.indeed.com/viewjob?jk=892431136a2962f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ad7ca6161e3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b965fc898d308c</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70943ce5f887ca8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd1e41d5949d150</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palomar College</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe8d5c4946b355</t>
+          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fdaab0a9b0d0cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EXECUTIVE - Senior Full Stack AI/Java Developer - Raleigh, NC</t>
+          <t>ETL Testing with Azure Databricks in Healthcare</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6954fce33a80b920</t>
+          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
+          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87747bfcd30cdbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer I-Software</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=137f20c09a8e5c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=75d602908669423e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c80e2086f0d108</t>
+          <t>https://www.indeed.com/viewjob?jk=10de5f0ca2f7673d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL Testing with Azure Databricks in Healthcare</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af37a4075a8760f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6750fd9ad4e72e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662840de4364e997</t>
+          <t>https://www.indeed.com/viewjob?jk=c45db6ac50eb5587</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d148fa8c6ae39fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0f7e27e90a87e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-1</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e40302b3b533bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dc81e5cd9b6b72</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud &amp; Systems Engineer</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Global Healing Center</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14fea47c1dbfabac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780638094f78620b</t>
+          <t>https://www.indeed.com/viewjob?jk=02d7bcc2bd0697b0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Software Engineer 2 - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fe0f50a558682d2</t>
+          <t>https://www.indeed.com/viewjob?jk=50e0ff85e5f89851</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>Global Healing Center</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
+          <t>AWS, Lambda, Step Functions, S3, SNS, API Gateway, IAM, Scala, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
+          <t>https://www.indeed.com/viewjob?jk=38ae1e7d38a178a6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, S3, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096d9e696ae3fadd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bfd917914d4728</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05780e87aea394</t>
+          <t>https://www.indeed.com/viewjob?jk=0da29d3af250447a</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, IT Solutions 1</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Celestica</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Data Modeling, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee982b6d11792f00</t>
+          <t>https://www.indeed.com/viewjob?jk=9672d81f2806d2a2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc18b55e9187d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1a799d8b14436a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571ca52ff80cfc56</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer, Financial &amp; Card Issuance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8f6d93b707b783</t>
+          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6006f51c65e9f139</t>
+          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205804a055fd2049</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c5706918e358a0</t>
+          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a398f9aeeb6c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8977f5b4ab10d23</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b71ab143505ef</t>
+          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640d49c55b368f21</t>
+          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37ce07d5d4393f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10aa5fc172c0cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a1d20202a2aef8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8185d403faf25e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a014ab60dbd75f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f103c6f8f1eabe61</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae886d34419a9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfd83638c49b733</t>
+          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db9bfc62c64e2</t>
+          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83814a502692afe0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7005ca8416f01f</t>
+          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616e989c777fcd64</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46aa375a4da0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6904e697ef07baaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc64b2070c5c6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7574e666ce713</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bc4057502816b</t>
+          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8810eb13c55de856</t>
+          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7372945ed1cbee22</t>
+          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06b4f714255d00b</t>
+          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81cd4c9bce9e715</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec639e703e1f70</t>
+          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7628f7ec7ab09a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d764f5358afc422f</t>
+          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95628c711a619430</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4e67862f3b9941</t>
+          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2963649fc0f492cf</t>
+          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b60449ed066d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c80024050212c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b032019de44f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0ff3586081cca1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1744462634cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f69babc93629c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ca948db3aefbff</t>
+          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61326d67184dc890</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f0c70aeab55966</t>
+          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f5e91eebbc9f06</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b8dad0cc443b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e348dae6016f17</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cf9334f4d71f83</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c6c1388c411eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d19e0ea73bf12c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f611a382e3aa720</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc1c1ddf5b07e8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Anaylst</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
+          <t>https://www.indeed.com/viewjob?jk=cab7b07d708701fa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Anaylst</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, Talend, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b13758862656b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f8a94ff9473b05</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Risk Developer (Python/Azure)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
+          <t>https://www.indeed.com/viewjob?jk=2698e1f59bd5def7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abcf8ec50a625bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0bc94cbe8822db</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Paterson, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=75f6d90e6b234f60</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e53f9ddcb5f4c2b9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Full-Stack Developer</t>
+          <t>ETL Developer / Data Warehouse Architect - 26-02123</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FullPath</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ff07c409bb7f44</t>
+          <t>https://www.indeed.com/viewjob?jk=44fb3987d11d1123</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Risk Developer (Python/Azure)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7762d03304071b69</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b260e746e7b9c233</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c08c735142c13e1b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5111,19 +5111,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b73f36e3384d3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5146,29 +5146,29 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
+          <t>https://www.indeed.com/viewjob?jk=21dda777f28ecb1c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,104 +5176,104 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e55ba38c1cf2b9</t>
+          <t>https://www.indeed.com/viewjob?jk=691b9789f526ed3f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer(61249-1)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vytwo Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c69b171e220ab97a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kapitus</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb33829bcae7129</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer(61249-1)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vytwo Technologies</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, Airflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b5fdd13d31dd0aa1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
+          <t>DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>APi Group, Inc.</t>
+          <t>Kapitus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New Brighton, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31099f3a1c434171</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
+          <t>https://www.indeed.com/viewjob?jk=29fd50cad36943ce</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Systems Engineer - Oracle Cloud Infrastructure (OCI)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>APi Group, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New Brighton, MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6450f77aa7cdc7c1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kafka Azure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, Kafka, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>Scala, Snowflake, Oracle, ETL, ELT, Power BI, Tableau, Jenkins, Jenkins, SQL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ee2712fc0c8c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1819f14826f577</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Azure Stack Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
+          <t>https://www.indeed.com/viewjob?jk=356ea556fe0d82a4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Azure Stack Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, Power BI, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=20dcbc83d5643838</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
+          <t>https://www.indeed.com/viewjob?jk=b109c86f55c8c21f</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, GCP, BigQuery, Vertex AI, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d6781b2e7b9433</t>
+          <t>https://www.indeed.com/viewjob?jk=0e134c7566cf151c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior Data Scientist - AI Practice Team</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Power BI, Tableau, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+          <t>https://www.indeed.com/viewjob?jk=540f72e9dcda8dc2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
+          <t>https://www.indeed.com/viewjob?jk=15ecc0cd2b5a2111</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Spark Streaming, Oracle, CI/CD</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8b8935c84e2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=739e08afe4ba1176</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
+          <t>https://www.indeed.com/viewjob?jk=151fe9868f44f2f1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Observability</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,17 +5736,52 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, Splunk, CI/CD, Docker, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08caee1edcf07e86</t>
+          <t>https://www.indeed.com/viewjob?jk=51cfcfbf2a1e5657</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b2c457ac06652a</t>
         </is>
       </c>
     </row>
